--- a/artfynd/A 54297-2020 artfynd.xlsx
+++ b/artfynd/A 54297-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 54297-2020 artfynd.xlsx
+++ b/artfynd/A 54297-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1397,6 +1397,130 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>115109563</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57388</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Ljusmyran SV Ljusträsket, Nb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>803831</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7327207</v>
+      </c>
+      <c r="S8" t="n">
+        <v>100</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Mats Bergquist</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Mats Bergquist, Frida Snell</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 54297-2020 artfynd.xlsx
+++ b/artfynd/A 54297-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1399,10 +1399,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>115109563</v>
+        <v>115307235</v>
       </c>
       <c r="B8" t="n">
-        <v>57414</v>
+        <v>56481</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1411,37 +1411,37 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>102613</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1481,22 +1481,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-03-10</t>
+          <t>2024-03-21</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-03-10</t>
+          <t>2024-03-21</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1516,134 +1516,10 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Mats Bergquist, Frida Snell</t>
+          <t>Mats Bergquist</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>115307235</v>
-      </c>
-      <c r="B9" t="n">
-        <v>56481</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>102613</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Orre</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Lyrurus tetrix</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Ljusmyran SV Ljusträsket, Nb</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>803831</v>
-      </c>
-      <c r="R9" t="n">
-        <v>7327207</v>
-      </c>
-      <c r="S9" t="n">
-        <v>100</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Boden</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Överluleå</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2024-03-21</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2024-03-21</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>Mats Bergquist</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Mats Bergquist</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 54297-2020 artfynd.xlsx
+++ b/artfynd/A 54297-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1521,6 +1521,130 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>125049175</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58227</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103056</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Videsparv</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Emberiza rustica</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Pallas, 1776</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ljusmyran SV Ljusträsket, Nb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>803831</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7327207</v>
+      </c>
+      <c r="S9" t="n">
+        <v>100</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Mats Bergquist</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Mats Bergquist</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 54297-2020 artfynd.xlsx
+++ b/artfynd/A 54297-2020 artfynd.xlsx
@@ -1526,7 +1526,7 @@
         <v>125049175</v>
       </c>
       <c r="B9" t="n">
-        <v>58227</v>
+        <v>58325</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
